--- a/数据表/Datas/DifficultyConfig_难度配置.xlsx
+++ b/数据表/Datas/DifficultyConfig_难度配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -38,7 +38,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>enemyParties</t>
+    <t>*enemyParties</t>
   </si>
   <si>
     <t>##type</t>
@@ -50,7 +50,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=|),WeightedEnemyParty#sep=,</t>
+    <t>list,WeightedEnemyParty</t>
   </si>
   <si>
     <t>##group</t>
@@ -59,6 +59,12 @@
     <t>c</t>
   </si>
   <si>
+    <t>partyId</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -68,13 +74,22 @@
     <t>显示名</t>
   </si>
   <si>
-    <t>按权重选择地图敌人队伍</t>
+    <t>敌人队伍配置ID</t>
+  </si>
+  <si>
+    <t>刷新权重</t>
   </si>
   <si>
     <t>Tier1</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>难度</t>
     </r>
     <r>
@@ -88,13 +103,16 @@
     </r>
   </si>
   <si>
-    <t>4001,70|4002,30</t>
-  </si>
-  <si>
     <t>Tier2</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>难度</t>
     </r>
     <r>
@@ -108,13 +126,16 @@
     </r>
   </si>
   <si>
-    <t>4002,50|4003,50</t>
-  </si>
-  <si>
     <t>Tier3</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>难度</t>
     </r>
     <r>
@@ -126,9 +147,6 @@
       </rPr>
       <t>3</t>
     </r>
-  </si>
-  <si>
-    <t>4003,50|4004,50</t>
   </si>
 </sst>
 </file>
@@ -346,7 +364,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,18 +421,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -564,7 +570,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -589,8 +595,60 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF9BBB9B"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9BBB9B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF9EBDD7"/>
       </left>
+      <right style="thin">
+        <color rgb="FF9EBDD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9EBDD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF9EBDD7"/>
       </right>
@@ -747,7 +805,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -771,7 +829,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -783,120 +841,120 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -908,31 +966,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1406,17 +1476,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="44.1176470588235" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="21.6911764705882" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.3529411764706" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1426,89 +1497,188 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="6"/>
     </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="5" t="s">
+    <row r="2" customHeight="1" spans="1:5">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="E2" s="10"/>
     </row>
-    <row r="3" customHeight="1" spans="1:4">
-      <c r="A3" s="7" t="s">
+    <row r="3" customHeight="1" spans="1:5">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="12" t="s">
         <v>9</v>
       </c>
+      <c r="E3" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" customHeight="1" spans="1:4">
-      <c r="A4" s="9" t="s">
+    <row r="4" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="1:5">
+      <c r="A5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
+      <c r="C5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:4">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>16</v>
+    <row r="6" customHeight="1" spans="1:5">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="16">
+        <v>4001</v>
+      </c>
+      <c r="E6" s="16">
+        <v>70</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="12" t="s">
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="16">
+        <v>4002</v>
+      </c>
+      <c r="E7" s="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:5">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:5">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:5">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="C10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="16">
+        <v>4002</v>
+      </c>
+      <c r="E10" s="16">
+        <v>50</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="13" t="s">
+    <row r="11" customHeight="1" spans="1:5">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16">
+        <v>4003</v>
+      </c>
+      <c r="E11" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:5">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:5">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:5">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:5">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="C15" s="17" t="s">
         <v>22</v>
+      </c>
+      <c r="D15" s="16">
+        <v>4003</v>
+      </c>
+      <c r="E15" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
+      <c r="D16" s="2">
+        <v>4004</v>
+      </c>
+      <c r="E16" s="16">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/数据表/Datas/DifficultyConfig_难度配置.xlsx
+++ b/数据表/Datas/DifficultyConfig_难度配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -59,7 +59,7 @@
     <t>c</t>
   </si>
   <si>
-    <t>partyId</t>
+    <t>threat</t>
   </si>
   <si>
     <t>weight</t>
@@ -74,7 +74,7 @@
     <t>显示名</t>
   </si>
   <si>
-    <t>敌人队伍配置ID</t>
+    <t>刷新敌人威胁度</t>
   </si>
   <si>
     <t>刷新权重</t>
@@ -103,6 +103,18 @@
     </r>
   </si>
   <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
     <t>Tier2</t>
   </si>
   <si>
@@ -159,7 +171,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -210,6 +222,12 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -808,153 +826,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1003,6 +1021,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1476,7 +1497,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1572,106 +1593,152 @@
       <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="16">
-        <v>4001</v>
+      <c r="D6" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="E6" s="16">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="16">
-        <v>4002</v>
+      <c r="D7" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="E7" s="16">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="D8" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="15"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="D9" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="16">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="15"/>
-      <c r="B10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="16">
-        <v>4002</v>
-      </c>
-      <c r="E10" s="16">
-        <v>50</v>
-      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16">
-        <v>4003</v>
+      <c r="B11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="E11" s="16">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="D12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="16">
+        <v>50</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="1:5">
       <c r="A13" s="15"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="16">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" customHeight="1" spans="1:5">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="D14" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="1:5">
       <c r="A15" s="15"/>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:5">
+      <c r="A17" s="15"/>
+      <c r="B17" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:5">
+      <c r="D18" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:5">
+      <c r="D19" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="E19" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:5">
+      <c r="D20" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="16">
-        <v>4003</v>
-      </c>
-      <c r="E15" s="16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:5">
-      <c r="D16" s="2">
-        <v>4004</v>
-      </c>
-      <c r="E16" s="16">
-        <v>50</v>
+      <c r="E20" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
